--- a/output/pdf_financials_xlsx/GFT.xlsx
+++ b/output/pdf_financials_xlsx/GFT.xlsx
@@ -1079,16 +1079,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.105099</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.011761</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.001856</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>3.306708</v>
       </c>
     </row>
     <row r="35">
@@ -1117,16 +1117,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.105099</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.011761</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.001856</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>3.306708</v>
       </c>
     </row>
     <row r="37">
@@ -1345,16 +1345,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.105099</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.011761</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.001856</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>3.326787</v>
+        <v>0.020079</v>
       </c>
     </row>
     <row r="49">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">

--- a/output/pdf_financials_xlsx/GFT.xlsx
+++ b/output/pdf_financials_xlsx/GFT.xlsx
@@ -1714,13 +1714,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.021166</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.0375</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.00814</v>
       </c>
       <c r="E67" s="3" t="n">
         <v>0</v>
@@ -2376,10 +2376,10 @@
         <v>0</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.0008</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.009754000000000001</v>
       </c>
     </row>
     <row r="102">
@@ -2471,10 +2471,10 @@
         <v>-0.032214</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.010426</v>
+        <v>-0.011226</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.07890800000000001</v>
+        <v>0.06915399999999999</v>
       </c>
     </row>
     <row r="107">
@@ -4502,7 +4502,11 @@
           <t>GST Receivable</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -4800,7 +4804,11 @@
           <t>Shares issued - private placement</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -5318,7 +5326,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
